--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -513,17 +513,17 @@
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -532,9 +532,9 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,10 +851,8 @@
           <t>Sandip Tamang</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9813373038</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9813373038</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9813373038</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9813373038</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -944,10 +940,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -958,32 +952,1059 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>2d 11h 40m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 9:56 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9808255039</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9808255039</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.69109</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>anilbeck052@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>03:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.288</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 9:55 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9808255039</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9808255039</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69109</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>anilbeck052@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>03:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.288</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 9:53 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Skycom to nettv change</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337623</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851056329</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:53:48 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851056329</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:47:11 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:53:48 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Rato Pull Tarkari bazar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 9:50 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337927</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:21 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:21 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:50:57 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders, MAKUTE PROFESSIONAL POWER TOOLS - Hardware store ?? ??????? ?????, Kathmandu 44600,</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>agchirag0811@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>18h 18m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>18h 18m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337707</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ishwar Upadhayay</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Ishwar Upadhayay</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9861493747</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:00:40 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841324413</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:05:47 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:00:40 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.70258</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Darshana School - Gothatar, Kageshwari Manohara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>i9841324413@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>06:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L28-4</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.37109</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>20h 54m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -998,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1035,7 +2056,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +2066,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1056,7 +2077,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1068,7 +2089,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>8h 42m</t>
         </is>
       </c>
     </row>
@@ -1080,7 +2101,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 40m</t>
+          <t>1d 4h 51m</t>
         </is>
       </c>
     </row>
@@ -1121,214 +2142,456 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1336234</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Sandip Tamang</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>2d 11h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337707</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Ishwar Upadhayay</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:00:40 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:05:47 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:00:40 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Anil Dawadi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9808255039</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9808255039</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9808255039</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9808255039</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1086,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.69109</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.69109</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1145,25 +1139,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.288</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.288</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1259,10 +1249,8 @@
           <t>Anil Dawadi</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9808255039</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9808255039</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1277,10 +1265,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9808255039</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9808255039</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1297,10 +1283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69109</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69109</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1356,25 +1340,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.288</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.288</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1470,10 +1450,8 @@
           <t>Dinesh Shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851056329</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851056329</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1488,10 +1466,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9851056329</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9851056329</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1555,10 +1531,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1569,7 +1543,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1665,10 +1639,8 @@
           <t>Madhav Traders</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9745867186</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9745867186</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1683,10 +1655,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9745867186</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9745867186</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1754,10 +1724,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1768,7 +1736,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1854,20 +1822,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Ishwar Upadhayay</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9861493747</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9861493747</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1882,10 +1844,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9841324413</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9841324413</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1902,10 +1862,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.70258</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.70258</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1961,25 +1919,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L28-4</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.37109</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.37109</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2028,7 +1982,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2427,7 +2381,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2494,7 +2448,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2561,7 +2515,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,23 +501,23 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1959,6 +1959,818 @@
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338368</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saloni kandel</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saloni kandel</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851047125</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:50:18 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851047125</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:10:17 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:50:18 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>M858+QXJ Lalitpur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>kandelshalikram2021@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>13h 40m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>router faulty</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338209</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Debaki Kuinkel</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Debaki Kuinkel</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841980108</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:35:33 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841980108</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 06:56:42 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:35:33 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.722969</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Chwassa jhol Momo Kageshwori Manohara 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>01:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L57-7</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.402984</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 38m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:55 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337920</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9761834602</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>KLK9761834602</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:55:28 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>ktm bhimeshthan , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>ranjit58@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB334</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>19h 29m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>19h 29m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337833</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841482102</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:28 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841482102S</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:28 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:53:15 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Ratna Rajya Sec. School, M8WP+7XM, Devkota Sadak, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>sumitrashrestha1444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L52-6</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>20h 2m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 2m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1973,16 +2785,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2010,7 +2822,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2020,7 +2832,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2031,7 +2843,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2855,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 42m</t>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2867,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 51m</t>
+          <t>1d 7m</t>
         </is>
       </c>
     </row>
@@ -2096,334 +2908,241 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2438,12 +3157,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2453,99 +3172,367 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338014</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Anil Dawadi</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:30:29 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:56:02 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1337707</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Ishwar Upadhayay</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>20h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338368</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Saloni kandel</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:50:18 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:10:17 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:50:18 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>13h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338209</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Debaki Kuinkel</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:35:33 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 06:56:42 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 10:35:33 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -2029,10 +2029,8 @@
           <t>Saloni kandel</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851047125</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851047125</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2104,10 +2102,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2126,10 +2122,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2140,7 +2134,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2236,10 +2230,8 @@
           <t>Debaki Kuinkel</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841980108</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841980108</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2274,10 +2266,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.722969</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.722969</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2329,25 +2319,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L57-7</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.402984</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.402984</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2443,10 +2429,8 @@
           <t>Uttam Ranjit</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9761834602</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9761834602</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2532,10 +2516,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2546,7 +2528,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2642,10 +2624,8 @@
           <t>Sumitra Shrestha</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841482102</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841482102</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2731,10 +2711,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -2745,32 +2723,454 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>20h 2m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 2m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>20h 2m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>20h 2m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade Router</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337837</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:26 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841974213G</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:51:57 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:06:02 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Kathmandu, Bagm</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>06:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB035</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:05 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade Router</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337837</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:26 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9841974213G</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:51:57 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:06:02 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Kathmandu, Bagm</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>06:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB035</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2785,11 +3185,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -2822,7 +3222,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2832,7 +3232,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2843,7 +3243,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2855,7 +3255,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 48m</t>
+          <t>9h 24m</t>
         </is>
       </c>
     </row>
@@ -2867,7 +3267,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
@@ -2908,14 +3308,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3002,14 +3402,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3835,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3502,14 +3902,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 10:35:33 AM</t>
@@ -3533,6 +3933,140 @@
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>15h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337837</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:26 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:51:57 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:06:02 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337837</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:26 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:51:57 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:06:02 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,7 +527,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -2819,10 +2819,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2857,10 +2855,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2916,25 +2912,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB035</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3030,10 +3022,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3068,10 +3058,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3127,50 +3115,671 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB035</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>20h 12m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337743</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9706418933</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>CHB9706418933</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:35:44 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Besi Gaun Gokarneshwor 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>sushanimagar00@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>07:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L15-4</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9766911015</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>BKT9766911015</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.675623234943277</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>bkt PepsiCola , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>hy6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>00:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L14-3</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.36926269531251</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9766911015</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>BKT9766911015</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.675623234943277</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>bkt PepsiCola , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>hy6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>00:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L14-3</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.36926269531251</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3222,7 +3831,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3232,7 +3841,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3243,7 +3852,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3864,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 24m</t>
+          <t>6h 50m</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3876,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>2d 18h 11m</t>
         </is>
       </c>
     </row>
@@ -3308,14 +3917,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -3402,14 +4011,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -3969,7 +4578,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -4036,14 +4645,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>18 Sep 2026 02:53:26 PM</t>
@@ -4067,6 +4676,207 @@
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>20h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337743</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:35:44 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3225,10 +3225,8 @@
           <t>Mina Rakaskoti</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9706418933</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9706418933</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3318,10 +3316,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3332,7 +3328,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3428,10 +3424,8 @@
           <t>hemat katuwal</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9766911015</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9766911015</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3466,10 +3460,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.675623234943277</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.67562323494328</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3525,25 +3517,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>L14-3</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.36926269531251</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.36926269531251</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3639,10 +3627,8 @@
           <t>hemat katuwal</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9766911015</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9766911015</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3677,10 +3663,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.675623234943277</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67562323494328</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3736,48 +3720,458 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L14-3</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.36926269531251</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.36926269531251</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337745</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Burger House</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Burger House</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9803922803</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>LTP9803922803</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:38:21 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Satdobato , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>Burgerhouse@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>08:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB052</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>10d 20h 30m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>22h 1m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337841</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:54:18 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841974213N</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:23 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:46:44 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Kathmandu, Bagm</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>06:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB035</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>20h 52m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3794,13 +4188,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3831,7 +4225,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3841,7 +4235,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3852,7 +4246,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -3864,7 +4258,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 50m</t>
+          <t>7h 23m</t>
         </is>
       </c>
     </row>
@@ -3876,7 +4270,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 18h 11m</t>
+          <t>2d 11h 18m</t>
         </is>
       </c>
     </row>
@@ -3917,14 +4311,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -3964,328 +4358,235 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>76.9%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4300,12 +4601,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4315,44 +4616,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4367,12 +4668,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -4382,44 +4683,44 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4434,12 +4735,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4449,54 +4750,54 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -4516,22 +4817,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4541,19 +4842,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4568,12 +4869,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4583,64 +4884,64 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -4650,44 +4951,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4702,59 +5003,59 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4769,114 +5070,382 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1337743</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:35:44 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:27:13 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1326845</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>hemat katuwal</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>10d 20h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337745</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Burger House</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:38:21 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>22h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337841</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:54:18 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:53:23 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:46:44 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>20h 52m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3830,10 +3830,8 @@
           <t>Burger House</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9803922803</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9803922803</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3923,10 +3921,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3937,7 +3933,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4033,10 +4029,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4071,10 +4065,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4130,48 +4122,1496 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>CDB035</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>20h 52m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>20h 52m</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>20h 53m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:59 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router / adapter faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router / adapter faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337920</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9761834602</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>KLK9761834602</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>ktm bhimeshthan , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>ranjit58@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>06:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB334</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>20h 24m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337920</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9761834602</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9761834602</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>ktm bhimeshthan , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>ranjit58@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>06:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB334</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>20h 24m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:48 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337834</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:02:48 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:40 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:48:35 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>06:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB036</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>20h 45m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>20h 57m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337562</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa magar</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa magar</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9861852500</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>KLK9861852500</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:55:24 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Budhanilkantha Municipality Ward No. 7 Office - Local government office Q84W+GR2 ????????? ??? ??? B</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9861852500@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>10:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L34-4</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54:29 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.7709</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Hello Kids Academy Montessori School Details from Google Maps Q9C3+32Q, Budhanilkantha 44600 , Bagma</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>pokharelnaba1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L15-8</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.3504</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54:29 AM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.7709</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Hello Kids Academy Montessori School Details from Google Maps Q9C3+32Q, Budhanilkantha 44600 , Bagma</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>pokharelnaba1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>07:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L15-8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.3504</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4188,7 +5628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4225,7 +5665,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -4235,7 +5675,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -4246,7 +5686,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +5698,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 23m</t>
+          <t>9h 38m</t>
         </is>
       </c>
     </row>
@@ -4270,7 +5710,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 18m</t>
+          <t>2d 5h 1m</t>
         </is>
       </c>
     </row>
@@ -4311,14 +5751,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -4376,351 +5816,246 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>78.6%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4735,12 +6070,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4750,44 +6085,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4802,12 +6137,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4817,44 +6152,44 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4869,12 +6204,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4884,54 +6219,54 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -4951,22 +6286,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4976,19 +6311,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5003,12 +6338,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5018,64 +6353,64 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5085,44 +6420,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5137,12 +6472,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -5152,44 +6487,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5204,12 +6539,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5219,44 +6554,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5286,22 +6621,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5311,29 +6646,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5348,27 +6683,27 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -5378,74 +6713,610 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>TKT1326845</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>hemat katuwal</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>08 Sep 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:28:05 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>10d 20h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337745</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Burger House</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:38:21 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:40:16 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>22h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>TKT1337841</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>20h 52m</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337920</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>20h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337920</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Ranjit</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:26:20 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:50:36 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>20h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337834</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:02:48 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:40 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:48:35 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>20h 45m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>20h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337562</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa magar</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:55:24 AM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54:29 AM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54:29 AM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -4335,10 +4335,8 @@
           <t>Uttam Ranjit</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9761834602</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9761834602</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4428,10 +4426,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4442,7 +4438,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4538,10 +4534,8 @@
           <t>Uttam Ranjit</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9761834602</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9761834602</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4631,10 +4625,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4645,7 +4637,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4741,10 +4733,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4779,10 +4769,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4838,25 +4826,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB036</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5055,10 +5039,8 @@
           <t>Bimala Thapa magar</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9861852500</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9861852500</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5130,10 +5112,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH24" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH24" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
@@ -5152,10 +5132,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5144,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5262,10 +5240,8 @@
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5300,10 +5276,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.7709</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.7709</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5359,25 +5333,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L15-8</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.3504</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.35039999999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5473,10 +5443,8 @@
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5511,10 +5479,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.7709</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.7709</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5570,50 +5536,866 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L15-8</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.3504</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.35039999999999</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>20h 39m</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>3d 2h 54m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:09 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338308</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 08:05:02 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:56:27 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:09:06 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Siddhicharan Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>16h 4m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>16h 12m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338274</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>subash karakheti</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>subash karakheti</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9866000653</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9866000653</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:36:45 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Gangalal hospital parking - Public parking space P8WR+3XF Bansbari Rd Kathmandu 44600, Kathmandu, Ne</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>02:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L20-7</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>16h 37m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>iptv youtube login issue</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338515</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9841200675</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:13:20 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9841200675</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:08:51 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:11 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.7114</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Nearby Big Mart P77G+2F5, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>agrawalnimesh71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.2781</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW26" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:13 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>iptv youtube login issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338515</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9841200675</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:13:20 AM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9841200675</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:08:51 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:11 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.7114</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Nearby Big Mart P77G+2F5, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>agrawalnimesh71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.2781</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -5628,13 +6410,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -5665,7 +6447,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -5675,7 +6457,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -5686,7 +6468,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -5698,7 +6480,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 38m</t>
+          <t>8h 41m</t>
         </is>
       </c>
     </row>
@@ -5710,7 +6492,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 1m</t>
+          <t>1d 22h 55m</t>
         </is>
       </c>
     </row>
@@ -5769,10 +6551,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -5787,14 +6569,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5805,14 +6587,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5896,7 +6678,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -5914,349 +6696,217 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6286,22 +6936,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -6311,19 +6961,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6338,12 +6988,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -6353,64 +7003,64 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6420,44 +7070,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6472,12 +7122,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -6487,44 +7137,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -6539,12 +7189,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -6554,54 +7204,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -6621,22 +7271,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6646,19 +7296,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -6673,12 +7323,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6688,44 +7338,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6740,12 +7390,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -6755,54 +7405,54 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6822,22 +7472,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -6847,19 +7497,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6874,12 +7524,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -6889,44 +7539,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -6951,27 +7601,27 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -6981,29 +7631,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7018,27 +7668,27 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7048,14 +7698,14 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -7085,49 +7735,49 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7142,59 +7792,59 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7209,114 +7859,516 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>TKT1337834</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:02:48 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:40 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:48:35 AM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>20h 45m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>20h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337562</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Bimala Thapa magar</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:06:12 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:55:24 AM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>1d 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>TKT1335308</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:54:29 AM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>20h 39m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>20h 39m</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>3d 2h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338274</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>subash karakheti</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:36:45 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>16h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338515</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:13:20 AM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:08:51 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:11 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338515</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:13:20 AM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:08:51 AM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:11 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5646,10 +5646,8 @@
           <t>Ishor Thapa</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9858052904</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9858052904</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5731,10 +5729,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5745,7 +5741,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5841,10 +5837,8 @@
           <t>subash karakheti</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9866000653</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9866000653</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5934,10 +5928,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5948,7 +5940,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6044,10 +6036,8 @@
           <t>Nirmal Agarwal</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9841200675</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9841200675</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6082,10 +6072,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.7114</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.7114</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6141,25 +6129,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.2781</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.27809999999999</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6255,10 +6239,8 @@
           <t>Nirmal Agarwal</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9841200675</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9841200675</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6293,10 +6275,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.7114</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.7114</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -6352,50 +6332,460 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.2781</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.27809999999999</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>4h 5m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338357</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9808035363</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:10:06 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>KLK9808035363</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 08:54:30 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:21:57 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>27.693722365366416, 85.2815403618628 GPS Coordinates Nearest: KAT004-01-3/7-ADB031 (114m Road) Map:</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>9808035363@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>3h 11m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>15h 27m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:20 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338277</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Mishra</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Mishra</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9840940417</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9840940417</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:20:02 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.713813</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>15,Kathmandu Metropolitan Near to Geetamata Community College,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>nirajanmishra5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.298172</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>16h 42m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>16h 42m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6419,7 +6809,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6447,7 +6837,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6468,7 +6858,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -6533,14 +6923,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -6583,113 +6973,108 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>85.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -6701,7 +7086,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -6719,23 +7104,23 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6747,300 +7132,212 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7055,12 +7352,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -7070,44 +7367,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7122,12 +7419,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -7137,44 +7434,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7189,12 +7486,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -7204,54 +7501,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7271,22 +7568,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7296,19 +7593,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7323,12 +7620,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -7338,64 +7635,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7405,44 +7702,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7457,12 +7754,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7472,44 +7769,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7524,12 +7821,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7539,44 +7836,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7606,22 +7903,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -7631,29 +7928,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7673,22 +7970,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7698,19 +7995,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7725,12 +8022,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7740,54 +8037,54 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -7807,22 +8104,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7832,19 +8129,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7859,12 +8156,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -7874,44 +8171,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7926,12 +8223,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -7941,44 +8238,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -7993,12 +8290,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -8008,44 +8305,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337834</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8075,44 +8372,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 03:02:48 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 02:50:40 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:48:35 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>20h 45m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>20h 57m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337562</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Bimala Thapa magar</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8142,121 +8439,121 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:55:24 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1338274</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>subash karakheti</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:36:45 PM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>16h 37m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -8271,102 +8568,236 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>TKT1338274</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>subash karakheti</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:36:45 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:09 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>16h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>TKT1338515</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Nirmal Agarwal</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:13:20 AM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:08:51 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:14:11 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338515</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Nirmal Agarwal</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>4h 5m</t>
         </is>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6442,10 +6442,8 @@
           <t>Saugat Kamal Upradi</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9808035363</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9808035363</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6480,10 +6478,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6535,25 +6531,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6649,10 +6641,8 @@
           <t>Nirajan Mishra</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9840940417</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9840940417</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6687,10 +6677,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.713813</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.713813</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6742,48 +6730,458 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>3,10</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.298172</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.29817199999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>16h 42m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>16h 42m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>16h 42m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>16h 42m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338578</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Puja Tamang</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Puja Tamang</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9803943162</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803943162</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:33:13 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Alfaz Mart P9JP+G5, Gokarneshwor 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>02:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L20-3</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>3h 10m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335508</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Ayushma Rani Singh</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Ayushma Rani Singh</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9843642240</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:35:36 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9843642240</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:09:20 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:35:36 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.67643</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Big Mart, Sahyoginagar,Koteshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>ayushmasingh19@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>07:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.33921</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 26m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6800,7 +7198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6809,7 +7207,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6837,7 +7235,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6847,7 +7245,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6858,7 +7256,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -6870,7 +7268,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 41m</t>
+          <t>7h 57m</t>
         </is>
       </c>
     </row>
@@ -6882,7 +7280,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 55m</t>
+          <t>1d 22h 12m</t>
         </is>
       </c>
     </row>
@@ -6923,14 +7321,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -7067,14 +7465,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -8803,6 +9201,140 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338578</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Puja Tamang</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:33:13 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>3h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335508</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Ayushma Rani Singh</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:35:36 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:09:20 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:35:36 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 26m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="31" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -6840,10 +6840,8 @@
           <t>Puja Tamang</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9803943162</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9803943162</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6933,10 +6931,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -6947,7 +6943,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7043,10 +7039,8 @@
           <t>Ayushma Rani Singh</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9843642240</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9843642240</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7081,10 +7075,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.67643</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.67643</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7140,48 +7132,665 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.33921</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.33920999999999</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 26m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:50 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Np internet connection</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338439</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Nipesh Khanal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Nipesh Khanal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9706745286</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:50:55 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>BKT9706745286</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:40:01 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:50:55 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Universal Driving Training Center - Driving school Madhyapur Thimi 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>nirmalnirmal8989@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>02:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Shrestha</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 26m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>10h 10m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Skycom to net TV</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338449</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9813761666</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:38:45 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9851244184</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:34:55 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:58:59 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.732722</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Ganga Hall Marg Kathmandu 44600 near by Kohinoor School - University, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>ss93official@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.304031</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>4h 20m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>6h 24m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:56 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338277</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Mishra</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Mishra</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9840940417</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9840940417</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:56:49 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.713813</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>15,Kathmandu Metropolitan Near to Geetamata Community College,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>nirajanmishra5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>03:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.298172</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>17h 18m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>17h 18m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7198,7 +7807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7235,7 +7844,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -7245,7 +7854,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -7256,7 +7865,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7877,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 57m</t>
+          <t>8h</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7889,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 12m</t>
+          <t>1d 19h 42m</t>
         </is>
       </c>
     </row>
@@ -7321,14 +7930,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7948,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7375,14 +7984,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7465,14 +8074,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -7484,18 +8093,18 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7507,7 +8116,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -7525,23 +8134,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7553,64 +8162,64 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7622,187 +8231,143 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7817,12 +8382,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -7832,32 +8397,32 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
@@ -7931,12 +8496,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -7951,12 +8516,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -7966,44 +8531,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8033,22 +8598,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8058,29 +8623,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -8100,22 +8665,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -8125,39 +8690,39 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -8167,32 +8732,32 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8831,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8286,12 +8851,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -8301,44 +8866,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8368,22 +8933,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -8393,7 +8958,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
@@ -8435,7 +9000,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -8467,22 +9032,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8502,22 +9067,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -8527,39 +9092,39 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -8569,44 +9134,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8621,12 +9186,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8636,32 +9201,32 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
@@ -8703,7 +9268,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -8735,12 +9300,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8755,12 +9320,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -8770,44 +9335,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337834</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8837,44 +9402,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:02:48 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 02:50:40 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:48:35 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 45m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 57m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337562</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Bimala Thapa magar</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -8904,32 +9469,32 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:55:24 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
@@ -9003,32 +9568,32 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1338274</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>subash karakheti</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9038,64 +9603,64 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:36:45 PM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>16h 37m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1338274</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>subash karakheti</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9105,32 +9670,32 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>18 Sep 2026 07:36:45 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>16h 37m</t>
         </is>
       </c>
     </row>
@@ -9204,134 +9769,335 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1338578</t>
+          <t>TKT1338515</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Puja Tamang</t>
+          <t>Nirmal Agarwal</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:33:13 AM</t>
+          <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>3h 10m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>TKT1338578</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Puja Tamang</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:33:13 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:44:07 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>3h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>TKT1335508</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Ayushma Rani Singh</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 11:09:20 AM</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>3d 1h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338439</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Nipesh Khanal</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:50:55 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:40:01 AM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:50:55 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>10h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338277</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Nirajan Mishra</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:37:56 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:56:49 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>17h 18m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>17h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7242,10 +7242,8 @@
           <t>Nipesh Khanal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9706745286</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9706745286</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7335,10 +7333,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7349,7 +7345,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7435,20 +7431,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr">
         <is>
           <t>Sadik Aakhtar Ansari</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9813761666</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9813761666</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7483,10 +7473,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.732722</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.732722</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7538,25 +7526,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.304031</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.30403099999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7652,10 +7636,8 @@
           <t>Nirajan Mishra</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9840940417</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9840940417</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7690,10 +7672,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.713813</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.713813</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7749,25 +7729,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>3,10</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.298172</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.29817199999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7816,7 +7792,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10000,7 +9976,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -10067,7 +10043,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7772,6 +7772,213 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:26 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338679</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:26:05 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.702095</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>P72Q+VQQ, Tahachal Marg, Kathmandu 44600 Near by Muna Dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>shresthanischit18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.289872</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>2h 4m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2h 4m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7820,7 +8027,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7841,7 +8048,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -7906,14 +8113,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -8050,14 +8257,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7839,10 +7839,8 @@
           <t>Nischit Shrestha</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9840184282</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9840184282</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7877,10 +7875,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.702095</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.702095</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7932,25 +7928,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.289872</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.289872</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7971,6 +7971,629 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:59 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="AA39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr"/>
+      <c r="W41" s="3" t="inlineStr"/>
+      <c r="X41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="AA41" s="3" t="inlineStr"/>
+      <c r="AB41" s="3" t="inlineStr"/>
+      <c r="AC41" s="3" t="inlineStr"/>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr"/>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr"/>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr"/>
+      <c r="AN41" s="3" t="inlineStr"/>
+      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="AA42" s="3" t="inlineStr"/>
+      <c r="AB42" s="3" t="inlineStr"/>
+      <c r="AC42" s="3" t="inlineStr"/>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr"/>
+      <c r="AF42" s="3" t="inlineStr"/>
+      <c r="AG42" s="3" t="inlineStr"/>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr"/>
+      <c r="AN42" s="3" t="inlineStr"/>
+      <c r="AO42" s="3" t="inlineStr"/>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337212</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Bharti</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Bharti</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9803165887</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:55:54 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9803165887</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:48:14 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:49:51 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu - Tokha Dhaneshwor Mandir - 3month(150Mbps)-Enquiry, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>bharatiniraj111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>13:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L9-4</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 1m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7982,7 +8605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7991,7 +8614,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8019,7 +8642,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -8029,7 +8652,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -8040,7 +8663,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8675,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>8h 29m</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8687,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 42m</t>
+          <t>1d 19h 36m</t>
         </is>
       </c>
     </row>
@@ -8105,14 +8728,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -8249,14 +8872,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -10276,6 +10899,73 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337212</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Bharti</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:55:54 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:48:14 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:49:51 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 1m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -8450,10 +8450,8 @@
           <t>Niraj Bharti</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9803165887</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9803165887</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8488,10 +8486,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8547,50 +8543,456 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L9-4</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 1m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>20h 53m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1d 17h 1m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338703</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Sakhham Lama</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Sakhham Lama</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9841577911</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:13:25 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9841577911</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:44:05 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:13:25 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.69975</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati ward no 13,Club Galli, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr"/>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>02:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB263</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.2984</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>no internet</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337939</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Rajdeep Shrestha</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Rajdeep Shrestha</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9851027165</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:57:41 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>CHB9761799695</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:38:38 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:57:41 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>basnatapur, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>rajdeepshre@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>08:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB084</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -8605,7 +9007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8642,7 +9044,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -8652,7 +9054,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -8663,7 +9065,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -8675,7 +9077,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 29m</t>
+          <t>7h 54m</t>
         </is>
       </c>
     </row>
@@ -8687,7 +9089,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 36m</t>
+          <t>1d 17h 27m</t>
         </is>
       </c>
     </row>
@@ -8728,14 +9130,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -8782,14 +9184,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8872,14 +9274,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -9010,14 +9412,14 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -10932,14 +11334,14 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 04:55:54 PM</t>
@@ -10963,6 +11365,140 @@
       <c r="M58" s="3" t="inlineStr">
         <is>
           <t>1d 17h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338703</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Sakhham Lama</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:13:25 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:44:05 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:13:25 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337939</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Rajdeep Shrestha</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:57:41 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:38:38 PM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:57:41 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8643,20 +8643,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Sakhham Lama</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9841577911</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9841577911</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8691,10 +8685,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.69975</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.69975</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8746,25 +8738,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>CDB263</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.2984</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.2984</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8860,10 +8848,8 @@
           <t>Rajdeep Shrestha</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9851027165</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9851027165</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8953,10 +8939,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -8967,32 +8951,661 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : no internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Slow issue</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338358</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Anjana pujari</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Anjana pujari</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9810168272</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:21:22 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>CHB9810168272</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 08:54:49 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:21:53 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>purano dhalko ganesh mandir, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>9810168272@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>04:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Pramod KC</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>22h 19m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>17h 27m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : no internet   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338064</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Gunaraj Karki</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Gunaraj Karki</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9841367945</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:18:29 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9841367945</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:03:11 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:18:29 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.70394</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Bira Complex, Newroad, Kathmandu  , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>07:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.31161</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>21h 15m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337596</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Pandit</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Pandit</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9843809706</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:26:10 AM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9843809706</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:26:10 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:26:34 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.759347</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Jarankhu Mart - Shopping mall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>sarjan.adhakari.111@gmil.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>13:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L14-3</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.304151</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9007,13 +9620,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -9044,7 +9657,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9054,7 +9667,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -9065,7 +9678,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9690,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 54m</t>
+          <t>8h</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9702,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 27m</t>
+          <t>1d 15h 37m</t>
         </is>
       </c>
     </row>
@@ -9130,14 +9743,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -9202,14 +9815,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9274,14 +9887,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -9435,14 +10048,14 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -9458,10 +10071,10 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -11401,7 +12014,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11468,14 +12081,14 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
           <t>Case : no internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Case : no internet   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 01:57:41 PM</t>
@@ -11499,6 +12112,207 @@
       <c r="M60" s="3" t="inlineStr">
         <is>
           <t>22h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338358</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Anjana pujari</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:21:22 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 08:54:49 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:21:53 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>17h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338064</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Gunaraj Karki</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:18:29 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:03:11 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:18:29 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>21h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337596</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Kalpana Pandit</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:26:10 AM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:26:10 AM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:26:34 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -9037,20 +9037,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>Anjana pujari</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9810168272</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9810168272</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9085,10 +9079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9144,25 +9136,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9258,10 +9246,8 @@
           <t>Gunaraj Karki</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9841367945</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9841367945</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9296,10 +9282,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.70394</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.70394</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9351,25 +9335,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.31161</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.31161</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9465,10 +9445,8 @@
           <t>Kalpana Pandit</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9843809706</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9843809706</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9503,10 +9481,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.759347</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.759347</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9562,50 +9538,671 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L14-3</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.304151</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.304151</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338736</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Pema Chodak</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Pema Chodak</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9840286296</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9840286296</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:03:46 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.72004</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>KFC Boudha,Boudhanath Sadak, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>pemachodak2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>02:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L43-5</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.35871</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:37 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338662</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Sabitri Rimal</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Sabitri Rimal</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841671731</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:07:25 AM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9841671731</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:07:25 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:37:42 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.7462</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, Kathmandu ,Near by Malpot Karyalaya, Manamaiju, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>sabitririmal5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.3126</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:36 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade the Router</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338071</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Narayan Maharjan</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Narayan Maharjan</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9849038761</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:46:42 AM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9801032326</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:11:13 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:36:19 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.69196</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Grande International Hospital - Private hospital Tokha Rd Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>maharjan.ran@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr"/>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L6-4</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.27525</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>2h 49m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>21h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -9620,7 +10217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9657,7 +10254,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9667,7 +10264,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -9678,7 +10275,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -9690,7 +10287,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>7h 46m</t>
         </is>
       </c>
     </row>
@@ -9702,7 +10299,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 37m</t>
+          <t>1d 14h 29m</t>
         </is>
       </c>
     </row>
@@ -9743,14 +10340,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -9887,14 +10484,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12745,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -12215,7 +12812,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -12282,14 +12879,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>18 Sep 2026 11:26:10 AM</t>
@@ -12313,6 +12910,73 @@
       <c r="M63" s="5" t="inlineStr">
         <is>
           <t>1d 3h</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338736</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Pema Chodak</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:03:46 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -9648,10 +9648,8 @@
           <t>Pema Chodak</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9840286296</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9840286296</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9686,10 +9684,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.72004</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.72004</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9745,25 +9741,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L43-5</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.35871</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.35871</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9859,10 +9851,8 @@
           <t>Sabitri Rimal</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841671731</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841671731</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9897,10 +9887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.7462</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.7462</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9952,25 +9940,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>3,10</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.3126</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.3126</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10066,10 +10050,8 @@
           <t>Narayan Maharjan</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9849038761</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9849038761</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10104,10 +10086,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.69196</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.69196</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10159,50 +10139,360 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L6-4</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.27525</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.27525</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>2h 49m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>21h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : Upgrade the Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>2h 49m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>21h 25m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : Upgrade the Router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338820</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Meera Kharel</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Meera Kharel</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9847252575</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:58:09 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9847252575</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:06:32 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:58:09 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.6943</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Chelsea International College, Lakhechaur Marg , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>kharel.meera@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>01:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L49-7</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.33517</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1h 51m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr"/>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" s="3" t="inlineStr"/>
+      <c r="W53" s="3" t="inlineStr"/>
+      <c r="X53" s="3" t="inlineStr"/>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr"/>
+      <c r="AA53" s="3" t="inlineStr"/>
+      <c r="AB53" s="3" t="inlineStr"/>
+      <c r="AC53" s="3" t="inlineStr"/>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr"/>
+      <c r="AF53" s="3" t="inlineStr"/>
+      <c r="AG53" s="3" t="inlineStr"/>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr"/>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr"/>
+      <c r="AM53" s="3" t="inlineStr"/>
+      <c r="AN53" s="3" t="inlineStr"/>
+      <c r="AO53" s="3" t="inlineStr"/>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10254,7 +10544,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -10264,7 +10554,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -10275,7 +10565,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -10287,7 +10577,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 46m</t>
+          <t>7h 32m</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10589,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 29m</t>
+          <t>1d 13h 25m</t>
         </is>
       </c>
     </row>
@@ -10340,14 +10630,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -10484,14 +10774,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -12946,14 +13236,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 02:39:48 PM</t>
@@ -12977,6 +13267,73 @@
       <c r="M64" s="3" t="inlineStr">
         <is>
           <t>2h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338820</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Meera Kharel</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:58:09 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:06:32 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:58:09 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>1h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10249,10 +10249,8 @@
           <t>Meera Kharel</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9847252575</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9847252575</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10287,10 +10285,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.6943</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.6943</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10346,25 +10342,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L49-7</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.33517</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.33517000000001</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10516,7 +10508,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13303,7 +13295,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10488,6 +10488,412 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338833</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9851136564</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851136564</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:30:31 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>P94C+8GF, Bhaimal Margh Chowk, Kathmandu 44600 near by Easy Mart, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>yatirajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L31-7</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>YouTube not working</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338726</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Maya shrestha</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Maya shrestha</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9766845753</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:21:01 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9860957539</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:58:53 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:21:01 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.707178</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Mahantar chowk gothatar , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>03:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr"/>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L29-5</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.371353</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3h 22m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10499,7 +10905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10508,7 +10914,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10536,7 +10942,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -10546,7 +10952,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -10557,7 +10963,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10975,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 32m</t>
+          <t>7h 19m</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10987,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 25m</t>
+          <t>1d 12h 26m</t>
         </is>
       </c>
     </row>
@@ -10622,14 +11028,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -10658,14 +11064,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10766,14 +11172,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>25</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -10877,14 +11283,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -10895,46 +11301,46 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -10946,187 +11352,143 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -11141,12 +11503,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -11156,32 +11518,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
@@ -11255,12 +11617,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -11275,12 +11637,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -11290,44 +11652,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11357,22 +11719,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -11382,29 +11744,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -11424,22 +11786,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -11449,39 +11811,39 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -11491,32 +11853,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
@@ -11590,12 +11952,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -11610,12 +11972,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -11625,44 +11987,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -11692,22 +12054,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -11717,7 +12079,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
@@ -11759,7 +12121,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -11791,22 +12153,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -11826,22 +12188,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -11851,39 +12213,39 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -11893,44 +12255,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11945,12 +12307,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -11960,32 +12322,32 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12389,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -12059,12 +12421,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -12079,12 +12441,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -12094,44 +12456,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337834</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12161,44 +12523,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:02:48 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 02:50:40 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:48:35 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 45m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 57m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337562</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Bimala Thapa magar</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -12228,32 +12590,32 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:55:24 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
@@ -12327,32 +12689,32 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1338274</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>subash karakheti</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -12362,64 +12724,64 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:36:45 PM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>16h 37m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1338274</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>subash karakheti</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -12429,32 +12791,32 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>18 Sep 2026 07:36:45 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>16h 37m</t>
         </is>
       </c>
     </row>
@@ -12528,32 +12890,32 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1338578</t>
+          <t>TKT1338515</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Puja Tamang</t>
+          <t>Nirmal Agarwal</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -12563,44 +12925,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:33:13 AM</t>
+          <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>3h 10m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1335508</t>
+          <t>TKT1338578</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Ayushma Rani Singh</t>
+          <t>Puja Tamang</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -12630,22 +12992,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:09:20 AM</t>
+          <t>19 Sep 2026 09:33:13 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -12655,29 +13017,29 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>3d 1h 26m</t>
+          <t>3h 10m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1338439</t>
+          <t>TKT1335508</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Nipesh Khanal</t>
+          <t>Ayushma Rani Singh</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -12697,22 +13059,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:40:01 AM</t>
+          <t>16 Sep 2026 11:09:20 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -12722,39 +13084,39 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>10h 10m</t>
+          <t>3d 1h 26m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1338277</t>
+          <t>TKT1338439</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Nirajan Mishra</t>
+          <t>Nipesh Khanal</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -12764,44 +13126,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>19 Sep 2026 02:40:01 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:56:49 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>10h 10m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1337212</t>
+          <t>TKT1338277</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Niraj Bharti</t>
+          <t>Nirajan Mishra</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12831,44 +13193,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:55:54 PM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>17 Sep 2026 08:48:14 PM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:49:51 PM</t>
+          <t>19 Sep 2026 12:56:49 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>17h 18m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 1m</t>
+          <t>17h 18m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1338703</t>
+          <t>TKT1337212</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Sakhham Lama</t>
+          <t>Niraj Bharti</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12883,12 +13245,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -12898,54 +13260,54 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>18 Sep 2026 04:55:54 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:44:05 AM</t>
+          <t>17 Sep 2026 08:48:14 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>19 Sep 2026 01:49:51 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 53m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>1d 17h 1m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1337939</t>
+          <t>TKT1338703</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Rajdeep Shrestha</t>
+          <t>Sakhham Lama</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -12965,22 +13327,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:38:38 PM</t>
+          <t>19 Sep 2026 11:44:05 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -12990,29 +13352,29 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>22h 19m</t>
+          <t>2h 29m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1338358</t>
+          <t>TKT1337939</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Anjana pujari</t>
+          <t>Rajdeep Shrestha</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -13032,22 +13394,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:22 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 08:54:49 PM</t>
+          <t>18 Sep 2026 03:38:38 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:53 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -13057,19 +13419,19 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>17h 27m</t>
+          <t>22h 19m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1338064</t>
+          <t>TKT1338358</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Gunaraj Karki</t>
+          <t>Anjana pujari</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -13079,7 +13441,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -13099,22 +13461,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 02:21:22 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 05:03:11 PM</t>
+          <t>18 Sep 2026 08:54:49 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 02:21:53 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -13124,39 +13486,39 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>21h 15m</t>
+          <t>17h 27m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1337596</t>
+          <t>TKT1338064</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Kalpana Pandit</t>
+          <t>Gunaraj Karki</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -13166,44 +13528,44 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>18 Sep 2026 05:03:11 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:26:34 PM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>21h 15m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1338736</t>
+          <t>TKT1337596</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Pema Chodak</t>
+          <t>Kalpana Pandit</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -13218,12 +13580,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -13233,99 +13595,233 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:03:46 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>19 Sep 2026 02:26:34 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>1d 3h</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>TKT1338736</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Pema Chodak</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:03:46 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:39:48 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>TKT1338820</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Meera Kharel</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 01:06:32 PM</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>1h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338726</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Maya shrestha</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:21:01 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:58:53 AM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:21:01 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>3h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW55"/>
+  <dimension ref="A1:AW61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -513,7 +513,7 @@
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -10555,10 +10555,8 @@
           <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9851136564</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9851136564</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10644,10 +10642,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10658,7 +10654,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10754,10 +10750,8 @@
           <t>Maya shrestha</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9766845753</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9766845753</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10792,10 +10786,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.707178</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.707178</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10847,50 +10839,968 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>L29-5</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.371353</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.371353</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3h 22m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
           <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:40 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" s="3" t="inlineStr"/>
+      <c r="W56" s="3" t="inlineStr"/>
+      <c r="X56" s="3" t="inlineStr"/>
+      <c r="Y56" s="3" t="inlineStr"/>
+      <c r="Z56" s="3" t="inlineStr"/>
+      <c r="AA56" s="3" t="inlineStr"/>
+      <c r="AB56" s="3" t="inlineStr"/>
+      <c r="AC56" s="3" t="inlineStr"/>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr"/>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr"/>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr"/>
+      <c r="AM56" s="3" t="inlineStr"/>
+      <c r="AN56" s="3" t="inlineStr"/>
+      <c r="AO56" s="3" t="inlineStr"/>
+      <c r="AP56" s="3" t="inlineStr"/>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : router collection   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:17 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr"/>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr"/>
+      <c r="AA57" s="3" t="inlineStr"/>
+      <c r="AB57" s="3" t="inlineStr"/>
+      <c r="AC57" s="3" t="inlineStr"/>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr"/>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr"/>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr"/>
+      <c r="AM57" s="3" t="inlineStr"/>
+      <c r="AN57" s="3" t="inlineStr"/>
+      <c r="AO57" s="3" t="inlineStr"/>
+      <c r="AP57" s="3" t="inlineStr"/>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:37 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr"/>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr"/>
+      <c r="V58" s="3" t="inlineStr"/>
+      <c r="W58" s="3" t="inlineStr"/>
+      <c r="X58" s="3" t="inlineStr"/>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr"/>
+      <c r="AA58" s="3" t="inlineStr"/>
+      <c r="AB58" s="3" t="inlineStr"/>
+      <c r="AC58" s="3" t="inlineStr"/>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr"/>
+      <c r="AF58" s="3" t="inlineStr"/>
+      <c r="AG58" s="3" t="inlineStr"/>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr"/>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr"/>
+      <c r="AM58" s="3" t="inlineStr"/>
+      <c r="AN58" s="3" t="inlineStr"/>
+      <c r="AO58" s="3" t="inlineStr"/>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:33 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:37:51 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:37:51 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.70417</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom,Chhauni, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>ravig4279@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr"/>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.2889</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>3h 22m</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338308</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:27:10 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:56:27 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:27:10 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Siddhicharan Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr"/>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>19h 30m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338776</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9841501537</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:24:11 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9841501537</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:29:31 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:24:11 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.699727</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Near S³ Music Academy, ?????????? ????? ?????, Kathmandu 44614, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>shresthasantosh853@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>CDB263</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.298917</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV55" s="3" t="inlineStr">
-        <is>
-          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW55" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -10905,7 +11815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10942,7 +11852,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -10952,7 +11862,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10963,7 +11873,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -10975,7 +11885,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 19m</t>
+          <t>7h 7m</t>
         </is>
       </c>
     </row>
@@ -10987,7 +11897,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 26m</t>
+          <t>1d 11h 31m</t>
         </is>
       </c>
     </row>
@@ -11028,14 +11938,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -11100,14 +12010,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -11172,14 +12082,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>25</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -11356,14 +12266,14 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -11379,10 +12289,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -13791,14 +14701,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
           <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 03:21:01 PM</t>
@@ -13822,6 +14732,73 @@
       <c r="M67" s="5" t="inlineStr">
         <is>
           <t>3h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338776</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:24:11 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:29:31 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:24:11 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW61"/>
+  <dimension ref="A1:AW65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11258,10 +11258,8 @@
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9849632777</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9849632777</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11296,10 +11294,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.70417</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.70417</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11351,25 +11347,21 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.2889</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.2889</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -11465,10 +11457,8 @@
           <t>Ishor Thapa</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9858052904</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9858052904</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -11550,10 +11540,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -11564,7 +11552,7 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -11660,10 +11648,8 @@
           <t>Santosh Shrestha</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9841501537</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9841501537</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -11698,10 +11684,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.699727</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.699727</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -11757,50 +11741,862 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>CDB263</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.298917</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.298917</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS61" s="3" t="inlineStr">
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335765</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9810170827</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9810170827</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:31:48 PM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>27.71201, 85.33701, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr"/>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>07:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>CDB024</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr"/>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT61" s="3" t="inlineStr">
-        <is>
-          <t>2h 54m</t>
-        </is>
-      </c>
-      <c r="AU61" s="3" t="inlineStr">
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV61" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW61" s="3" t="inlineStr">
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9842684993</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:38:58 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>BKT9842684993</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:56:36 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Futsal - Futsal court MC96+P25 Araniko Highway Suryabinayak 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>9842684993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr"/>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr"/>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>1h 17m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338801</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9841479134</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9841479134</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:06 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.72781</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Near Bhanubhakta Memorial School, Panipokhari, Shibungal Galli, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr"/>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>03:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.32481</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338801</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9841479134</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9841479134</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:06 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>27.72781</t>
+        </is>
+      </c>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Near Bhanubhakta Memorial School, Panipokhari, Shibungal Galli, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr"/>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>03:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>85.32481</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -11815,7 +12611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11852,7 +12648,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -11862,7 +12658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -11873,7 +12669,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -11885,7 +12681,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 7m</t>
+          <t>6h 43m</t>
         </is>
       </c>
     </row>
@@ -11897,7 +12693,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 11h 31m</t>
+          <t>1d 10h 49m</t>
         </is>
       </c>
     </row>
@@ -11938,14 +12734,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -12010,14 +12806,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -12082,14 +12878,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -12289,14 +13085,14 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -14768,14 +15564,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 03:24:11 PM</t>
@@ -14799,6 +15595,207 @@
       <c r="M68" s="3" t="inlineStr">
         <is>
           <t>2h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335765</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:31:48 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>3d 1h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338801</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:06 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338801</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:06 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11851,10 +11851,8 @@
           <t>M.d  talibakhtar</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9810170827</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9810170827</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -11922,10 +11920,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH62" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH62" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
@@ -11944,10 +11940,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
@@ -11958,7 +11952,7 @@
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -12054,10 +12048,8 @@
           <t>Kalpana Baral</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9842684993</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9842684993</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -12143,10 +12135,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -12157,7 +12147,7 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -12253,10 +12243,8 @@
           <t>Arpan Bahadur Singh</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9841479134</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9841479134</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -12291,10 +12279,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.72781</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.72781</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -12346,25 +12332,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.32481</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.32481</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -12460,10 +12442,8 @@
           <t>Arpan Bahadur Singh</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9841479134</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9841479134</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -12498,10 +12478,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y65" s="3" t="inlineStr">
-        <is>
-          <t>27.72781</t>
-        </is>
+      <c r="Y65" s="3" t="n">
+        <v>27.72781</v>
       </c>
       <c r="Z65" s="3" t="inlineStr">
         <is>
@@ -12553,25 +12531,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP65" s="3" t="inlineStr">
-        <is>
-          <t>85.32481</t>
-        </is>
+      <c r="AP65" s="3" t="n">
+        <v>85.32481</v>
       </c>
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
@@ -12620,7 +12594,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -15631,7 +15605,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -15698,7 +15672,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -15765,7 +15739,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW65"/>
+  <dimension ref="A1:AW66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12574,6 +12574,209 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>configure issue</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338779</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Tenjin Tamang</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Tenjin Tamang</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9863195256</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>9840900396</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:31:41 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Tinchuli Chowk - Multi-unit residential building - Kathmandu Metropolitan, Kathmandu, Bagmati, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>tenjinsangbu@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 2.4Ghz</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>04:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>L64-3</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr"/>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12585,7 +12788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12594,7 +12797,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12622,7 +12825,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -12632,7 +12835,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -12643,7 +12846,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12858,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 43m</t>
+          <t>6h 33m</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12870,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 10h 49m</t>
+          <t>1d 10h 3m</t>
         </is>
       </c>
     </row>
@@ -12792,97 +12995,92 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>75.7%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -12894,18 +13092,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -12917,7 +13115,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -12935,23 +13133,23 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -12963,18 +13161,18 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -12986,14 +13184,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -13004,46 +13202,46 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -13055,254 +13253,166 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 2.4Ghz</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1338014</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Anil Dawadi</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -13317,12 +13427,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -13332,44 +13442,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -13384,12 +13494,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -13399,44 +13509,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -13451,12 +13561,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -13466,54 +13576,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -13533,22 +13643,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -13558,19 +13668,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -13585,12 +13695,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -13600,64 +13710,64 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -13667,44 +13777,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -13719,12 +13829,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -13734,44 +13844,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -13786,12 +13896,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -13801,44 +13911,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -13868,22 +13978,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -13893,29 +14003,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -13935,22 +14045,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -13960,19 +14070,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -13987,12 +14097,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -14002,54 +14112,54 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -14069,22 +14179,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -14094,19 +14204,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -14121,12 +14231,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -14136,44 +14246,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -14188,12 +14298,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -14203,44 +14313,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -14255,12 +14365,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -14270,44 +14380,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337834</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -14337,44 +14447,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 03:02:48 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 02:50:40 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:48:35 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>20h 45m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>20h 57m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337562</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Bimala Thapa magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -14404,64 +14514,64 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:55:24 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1338274</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>subash karakheti</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -14471,54 +14581,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:36:45 PM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>16h 37m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14538,64 +14648,64 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1338274</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>subash karakheti</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -14605,64 +14715,64 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>18 Sep 2026 07:36:45 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>16h 37m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1338578</t>
+          <t>TKT1338515</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Puja Tamang</t>
+          <t>Nirmal Agarwal</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -14672,64 +14782,64 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:33:13 AM</t>
+          <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>3h 10m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1335508</t>
+          <t>TKT1338515</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Ayushma Rani Singh</t>
+          <t>Nirmal Agarwal</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -14739,54 +14849,54 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:09:20 AM</t>
+          <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 26m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1338439</t>
+          <t>TKT1338578</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Nipesh Khanal</t>
+          <t>Puja Tamang</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14806,22 +14916,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:40:01 AM</t>
+          <t>19 Sep 2026 09:33:13 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -14831,19 +14941,19 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>10h 10m</t>
+          <t>3h 10m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1338277</t>
+          <t>TKT1335508</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Nirajan Mishra</t>
+          <t>Ayushma Rani Singh</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -14858,12 +14968,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -14873,64 +14983,64 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>16 Sep 2026 11:09:20 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:56:49 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>3d 1h 26m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1337212</t>
+          <t>TKT1338439</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Niraj Bharti</t>
+          <t>Nipesh Khanal</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -14940,44 +15050,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:55:54 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>17 Sep 2026 08:48:14 PM</t>
+          <t>19 Sep 2026 02:40:01 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:49:51 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 17h 1m</t>
+          <t>10h 10m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1338703</t>
+          <t>TKT1338277</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Sakhham Lama</t>
+          <t>Nirajan Mishra</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -14992,12 +15102,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -15007,64 +15117,64 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:44:05 AM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>19 Sep 2026 12:56:49 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 18m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>17h 18m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1337939</t>
+          <t>TKT1337212</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Rajdeep Shrestha</t>
+          <t>Niraj Bharti</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -15074,54 +15184,54 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>18 Sep 2026 04:55:54 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:38:38 PM</t>
+          <t>17 Sep 2026 08:48:14 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>19 Sep 2026 01:49:51 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 53m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>22h 19m</t>
+          <t>1d 17h 1m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1338358</t>
+          <t>TKT1338703</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Anjana pujari</t>
+          <t>Sakhham Lama</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -15141,22 +15251,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:22 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 08:54:49 PM</t>
+          <t>19 Sep 2026 11:44:05 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:53 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -15166,29 +15276,29 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>17h 27m</t>
+          <t>2h 29m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1338064</t>
+          <t>TKT1337939</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Gunaraj Karki</t>
+          <t>Rajdeep Shrestha</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15208,22 +15318,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 05:03:11 PM</t>
+          <t>18 Sep 2026 03:38:38 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -15233,39 +15343,39 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>21h 15m</t>
+          <t>22h 19m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1337596</t>
+          <t>TKT1338358</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Kalpana Pandit</t>
+          <t>Anjana pujari</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -15275,54 +15385,54 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>19 Sep 2026 02:21:22 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>18 Sep 2026 08:54:49 PM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:26:34 PM</t>
+          <t>19 Sep 2026 02:21:53 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>17h 27m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1338736</t>
+          <t>TKT1338064</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Pema Chodak</t>
+          <t>Gunaraj Karki</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15342,22 +15452,22 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:03:46 PM</t>
+          <t>18 Sep 2026 05:03:11 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -15367,19 +15477,19 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>21h 15m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1338820</t>
+          <t>TKT1337596</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Meera Kharel</t>
+          <t>Kalpana Pandit</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -15394,12 +15504,12 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -15409,54 +15519,54 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:58:09 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:06:32 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:58:09 PM</t>
+          <t>19 Sep 2026 02:26:34 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1h 51m</t>
+          <t>1d 3h</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1338726</t>
+          <t>TKT1338736</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Maya shrestha</t>
+          <t>Pema Chodak</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15476,22 +15586,22 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:21:01 PM</t>
+          <t>19 Sep 2026 02:39:48 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:58:53 AM</t>
+          <t>19 Sep 2026 12:03:46 PM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:21:01 PM</t>
+          <t>19 Sep 2026 02:39:48 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -15501,29 +15611,29 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>3h 22m</t>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1338776</t>
+          <t>TKT1338820</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Meera Kharel</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -15543,22 +15653,22 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:24:11 PM</t>
+          <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:29:31 PM</t>
+          <t>19 Sep 2026 01:06:32 PM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:24:11 PM</t>
+          <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -15568,29 +15678,29 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2h 54m</t>
+          <t>1h 51m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1335765</t>
+          <t>TKT1338726</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>M.d  talibakhtar</t>
+          <t>Maya shrestha</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15610,22 +15720,22 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:29 PM</t>
+          <t>19 Sep 2026 03:21:01 PM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:31:48 PM</t>
+          <t>19 Sep 2026 11:58:53 AM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:29 PM</t>
+          <t>19 Sep 2026 03:21:01 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -15635,39 +15745,39 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>3d 1h 29m</t>
+          <t>3h 22m</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TKT1338801</t>
+          <t>TKT1338776</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Arpan Bahadur Singh</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -15677,99 +15787,300 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:53:26 PM</t>
+          <t>19 Sep 2026 03:24:11 PM</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:53:26 PM</t>
+          <t>19 Sep 2026 12:29:31 PM</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:06 PM</t>
+          <t>19 Sep 2026 03:24:11 PM</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>3h 7m</t>
+          <t>2h 54m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
+          <t>TKT1335765</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:31:48 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:29 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>3d 1h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>TKT1338801</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Arpan Bahadur Singh</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 12:53:26 PM</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 12:53:26 PM</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 04:01:06 PM</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>3h 7m</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M72" s="3" t="inlineStr">
         <is>
           <t>3h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338801</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Arpan Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:53:26 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:01:06 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>3h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338779</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Tenjin Tamang</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 2.4Ghz</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:31:41 PM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW66"/>
+  <dimension ref="A1:AW67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12641,10 +12641,8 @@
           <t>Tenjin Tamang</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9863195256</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9863195256</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -12734,10 +12732,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
@@ -12748,32 +12744,243 @@
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
           <t>Case : configure issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS66" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT66" s="3" t="inlineStr">
-        <is>
-          <t>4h 2m</t>
-        </is>
-      </c>
-      <c r="AU66" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV66" s="3" t="inlineStr">
-        <is>
-          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW66" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337949</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Prasad Bhattarai</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Prasad Bhattarai</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9851043882</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:46:45 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9851043882</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:46:45 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:01:21 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.697869</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Dhungeadda Pipalbot ( ??????????? ???????) , Gandaki Electronics Details from Google Maps M7RG+F8J,</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr"/>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>11:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>CDB531</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.329614</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12825,7 +13032,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -12835,7 +13042,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -12846,7 +13053,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -12858,7 +13065,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 33m</t>
+          <t>7h 1m</t>
         </is>
       </c>
     </row>
@@ -12870,7 +13077,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 10h 3m</t>
+          <t>1d 9h 50m</t>
         </is>
       </c>
     </row>
@@ -12911,14 +13118,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -13073,14 +13280,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -16050,14 +16257,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
           <t>Case : configure issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 04:33:53 PM</t>
@@ -16081,6 +16288,73 @@
       <c r="M74" s="3" t="inlineStr">
         <is>
           <t>4h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337949</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Suresh Prasad Bhattarai</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:46:45 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:46:45 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:01:21 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW67"/>
+  <dimension ref="A1:AW70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
@@ -12840,10 +12840,8 @@
           <t>Suresh Prasad Bhattarai</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9851043882</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9851043882</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -12878,10 +12876,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.697869</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.697869</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -12937,48 +12933,673 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>CDB531</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.329614</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.32961400000001</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS67" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 14m</t>
-        </is>
-      </c>
-      <c r="AT67" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 14m</t>
-        </is>
-      </c>
-      <c r="AU67" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV67" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338977</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Nunulal Shah</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Nunulal Shah</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9851013999</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:02 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9851013999</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:38 PM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:02 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr"/>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>Near 27.65874, 85.3532, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>nunulalshah999@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>01:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr"/>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>1h 36m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:12 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1331958</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Sangita kunwar</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Sangita kunwar</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9843445345</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02: 00:00 PM</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>KLK9843445345</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 07:07:10 AM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr"/>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>near by Caffè Dè Mandala - Restaurant M7FC+GP5 Kirtipur 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>9843445345@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>09:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>CDB225</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr"/>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>6d 10h 7m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338823</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:29 PM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:07:00 PM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:29 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>27.73269</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Kharibot, Siddhartha tol-16, Next to Simon Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr">
+        <is>
+          <t>bhattaspandan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr">
+        <is>
+          <t>04:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>85.29153</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>4h 3m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -12995,7 +13616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13032,7 +13653,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -13042,7 +13663,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -13053,7 +13674,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13686,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 1m</t>
+          <t>6h 41m</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13698,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 9h 50m</t>
+          <t>1d 8h 24m</t>
         </is>
       </c>
     </row>
@@ -13118,14 +13739,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -13172,14 +13793,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -13280,14 +13901,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -13455,23 +14076,23 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -13483,210 +14104,166 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 2.4Ghz</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 2.4Ghz</t>
+        </is>
+      </c>
       <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1336234</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Sandip Tamang</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:46:21 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:26:28 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>2d 11h 40m</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1338014</t>
+          <t>TKT1336234</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Anil Dawadi</t>
+          <t>Sandip Tamang</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -13701,12 +14278,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -13716,32 +14293,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:30:29 PM</t>
+          <t>16 Sep 2026 09:46:21 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:56:02 AM</t>
+          <t>19 Sep 2026 09:26:28 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>2d 11h 40m</t>
         </is>
       </c>
     </row>
@@ -13815,12 +14392,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1337707</t>
+          <t>TKT1338014</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Ishwar Upadhayay</t>
+          <t>Anil Dawadi</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -13835,12 +14412,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -13850,44 +14427,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:05:47 PM</t>
+          <t>18 Sep 2026 04:30:29 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:00:40 AM</t>
+          <t>19 Sep 2026 09:56:02 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 25m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 54m</t>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1338368</t>
+          <t>TKT1337707</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Saloni kandel</t>
+          <t>Ishwar Upadhayay</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -13917,22 +14494,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 09:10:17 PM</t>
+          <t>18 Sep 2026 01:05:47 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:50:18 AM</t>
+          <t>19 Sep 2026 10:00:40 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -13942,29 +14519,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>13h 40m</t>
+          <t>20h 54m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1338209</t>
+          <t>TKT1338368</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Debaki Kuinkel</t>
+          <t>Saloni kandel</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -13984,22 +14561,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 06:56:42 PM</t>
+          <t>18 Sep 2026 09:10:17 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 10:35:33 AM</t>
+          <t>19 Sep 2026 10:50:18 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -14009,39 +14586,39 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>15h 38m</t>
+          <t>13h 40m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1337837</t>
+          <t>TKT1338209</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Debaki Kuinkel</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -14051,32 +14628,32 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
+          <t>Case : router faulty  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:26 PM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:51:57 PM</t>
+          <t>18 Sep 2026 06:56:42 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:06:02 AM</t>
+          <t>19 Sep 2026 10:35:33 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>20h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>15h 38m</t>
         </is>
       </c>
     </row>
@@ -14150,12 +14727,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1337743</t>
+          <t>TKT1337837</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Mina Rakaskoti</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14170,12 +14747,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -14185,44 +14762,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Upgrade Router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>18 Sep 2026 02:53:26 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:35:44 PM</t>
+          <t>18 Sep 2026 02:51:57 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:27:13 AM</t>
+          <t>19 Sep 2026 11:06:02 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 12m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>21h 51m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1326845</t>
+          <t>TKT1337743</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>hemat katuwal</t>
+          <t>Mina Rakaskoti</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -14252,22 +14829,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>08 Sep 2026 02:57:40 PM</t>
+          <t>18 Sep 2026 01:35:44 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:28:05 AM</t>
+          <t>19 Sep 2026 11:27:13 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -14277,7 +14854,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>10d 20h 30m</t>
+          <t>21h 51m</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14896,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -14351,22 +14928,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1337745</t>
+          <t>TKT1326845</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Burger House</t>
+          <t>hemat katuwal</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -14386,22 +14963,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 01:38:21 PM</t>
+          <t>08 Sep 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:40:16 AM</t>
+          <t>19 Sep 2026 11:28:05 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -14411,39 +14988,39 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>22h 1m</t>
+          <t>10d 20h 30m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1337841</t>
+          <t>TKT1337745</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Burger House</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -14453,44 +15030,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:54:18 PM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:53:23 PM</t>
+          <t>18 Sep 2026 01:38:21 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:46:44 AM</t>
+          <t>19 Sep 2026 11:40:16 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>22h 1m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1337920</t>
+          <t>TKT1337841</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Uttam Ranjit</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -14505,12 +15082,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -14520,32 +15097,32 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>18 Sep 2026 02:54:18 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:26:20 PM</t>
+          <t>18 Sep 2026 02:53:23 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:50:36 AM</t>
+          <t>19 Sep 2026 11:46:44 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 52m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>20h 24m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
@@ -14587,7 +15164,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -14619,12 +15196,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1337834</t>
+          <t>TKT1337920</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+          <t>Uttam Ranjit</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -14639,12 +15216,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -14654,44 +15231,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:02:48 PM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 02:50:40 PM</t>
+          <t>18 Sep 2026 03:26:20 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:48:35 AM</t>
+          <t>19 Sep 2026 11:50:36 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>20h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>20h 57m</t>
+          <t>20h 24m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1337562</t>
+          <t>TKT1337834</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Bimala Thapa magar</t>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -14721,44 +15298,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 03:02:48 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:06:12 AM</t>
+          <t>18 Sep 2026 02:50:40 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:55:24 AM</t>
+          <t>19 Sep 2026 11:48:35 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 45m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 49m</t>
+          <t>20h 57m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1335308</t>
+          <t>TKT1337562</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Nabaraj Pokharel</t>
+          <t>Bimala Thapa magar</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -14788,32 +15365,32 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:14:39 PM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 08:59:52 AM</t>
+          <t>18 Sep 2026 11:06:12 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:54:29 AM</t>
+          <t>19 Sep 2026 11:55:24 AM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>20h 39m</t>
+          <t>1d 49m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 54m</t>
+          <t>1d 49m</t>
         </is>
       </c>
     </row>
@@ -14887,32 +15464,32 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1338274</t>
+          <t>TKT1335308</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>subash karakheti</t>
+          <t>Nabaraj Pokharel</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -14922,64 +15499,64 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>18 Sep 2026 03:14:39 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:36:45 PM</t>
+          <t>16 Sep 2026 08:59:52 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:09 PM</t>
+          <t>19 Sep 2026 11:54:29 AM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 39m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>16h 37m</t>
+          <t>3d 2h 54m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1338515</t>
+          <t>TKT1338274</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Nirmal Agarwal</t>
+          <t>subash karakheti</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -14989,32 +15566,32 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:13:20 AM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:08:51 AM</t>
+          <t>18 Sep 2026 07:36:45 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:14:11 PM</t>
+          <t>19 Sep 2026 12:14:09 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>16h 37m</t>
         </is>
       </c>
     </row>
@@ -15088,32 +15665,32 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1338578</t>
+          <t>TKT1338515</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Puja Tamang</t>
+          <t>Nirmal Agarwal</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -15123,44 +15700,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv youtube login issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 08:13:20 AM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:33:13 AM</t>
+          <t>19 Sep 2026 08:08:51 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:44:07 PM</t>
+          <t>19 Sep 2026 12:14:11 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>3h 10m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1335508</t>
+          <t>TKT1338578</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Ayushma Rani Singh</t>
+          <t>Puja Tamang</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -15190,22 +15767,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:09:20 AM</t>
+          <t>19 Sep 2026 09:33:13 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:35:36 PM</t>
+          <t>19 Sep 2026 12:44:07 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -15215,29 +15792,29 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 26m</t>
+          <t>3h 10m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1338439</t>
+          <t>TKT1335508</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Nipesh Khanal</t>
+          <t>Ayushma Rani Singh</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15257,22 +15834,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:40:01 AM</t>
+          <t>16 Sep 2026 11:09:20 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:50:55 PM</t>
+          <t>19 Sep 2026 12:35:36 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -15282,39 +15859,39 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>10h 10m</t>
+          <t>3d 1h 26m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1338277</t>
+          <t>TKT1338439</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Nirajan Mishra</t>
+          <t>Nipesh Khanal</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -15324,44 +15901,44 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Np internet connection   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:37:56 PM</t>
+          <t>19 Sep 2026 02:40:01 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:56:49 PM</t>
+          <t>19 Sep 2026 12:50:55 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>17h 18m</t>
+          <t>10h 10m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1337212</t>
+          <t>TKT1338277</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Niraj Bharti</t>
+          <t>Nirajan Mishra</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -15391,44 +15968,44 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 04:55:54 PM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>17 Sep 2026 08:48:14 PM</t>
+          <t>18 Sep 2026 07:37:56 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:49:51 PM</t>
+          <t>19 Sep 2026 12:56:49 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>17h 18m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 17h 1m</t>
+          <t>17h 18m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1338703</t>
+          <t>TKT1337212</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Sakhham Lama</t>
+          <t>Niraj Bharti</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -15443,12 +16020,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -15458,54 +16035,54 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>18 Sep 2026 04:55:54 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:44:05 AM</t>
+          <t>17 Sep 2026 08:48:14 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:13:25 PM</t>
+          <t>19 Sep 2026 01:49:51 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 53m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>1d 17h 1m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1337939</t>
+          <t>TKT1338703</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Rajdeep Shrestha</t>
+          <t>Sakhham Lama</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15525,22 +16102,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : no internet   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 03:38:38 PM</t>
+          <t>19 Sep 2026 11:44:05 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:57:41 PM</t>
+          <t>19 Sep 2026 02:13:25 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -15550,29 +16127,29 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>22h 19m</t>
+          <t>2h 29m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1338358</t>
+          <t>TKT1337939</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Anjana pujari</t>
+          <t>Rajdeep Shrestha</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -15592,22 +16169,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
+          <t>Case : no internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:22 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 08:54:49 PM</t>
+          <t>18 Sep 2026 03:38:38 PM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:21:53 PM</t>
+          <t>19 Sep 2026 01:57:41 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -15617,19 +16194,19 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>17h 27m</t>
+          <t>22h 19m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1338064</t>
+          <t>TKT1338358</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Gunaraj Karki</t>
+          <t>Anjana pujari</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -15639,7 +16216,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15659,22 +16236,22 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Slow issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 02:21:22 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 05:03:11 PM</t>
+          <t>18 Sep 2026 08:54:49 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:18:29 PM</t>
+          <t>19 Sep 2026 02:21:53 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -15684,39 +16261,39 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>21h 15m</t>
+          <t>17h 27m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1337596</t>
+          <t>TKT1338064</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Kalpana Pandit</t>
+          <t>Gunaraj Karki</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -15726,44 +16303,44 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 11:26:10 AM</t>
+          <t>18 Sep 2026 05:03:11 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:26:34 PM</t>
+          <t>19 Sep 2026 02:18:29 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1d 3h</t>
+          <t>21h 15m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1338736</t>
+          <t>TKT1337596</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Pema Chodak</t>
+          <t>Kalpana Pandit</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -15778,12 +16355,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -15793,44 +16370,44 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:03:46 PM</t>
+          <t>18 Sep 2026 11:26:10 AM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:39:48 PM</t>
+          <t>19 Sep 2026 02:26:34 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>1d 3h</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1338820</t>
+          <t>TKT1338736</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Meera Kharel</t>
+          <t>Pema Chodak</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -15860,22 +16437,22 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:58:09 PM</t>
+          <t>19 Sep 2026 02:39:48 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:06:32 PM</t>
+          <t>19 Sep 2026 12:03:46 PM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:58:09 PM</t>
+          <t>19 Sep 2026 02:39:48 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -15885,29 +16462,29 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1h 51m</t>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1338726</t>
+          <t>TKT1338820</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Maya shrestha</t>
+          <t>Meera Kharel</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15927,22 +16504,22 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router instal   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:21:01 PM</t>
+          <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:58:53 AM</t>
+          <t>19 Sep 2026 01:06:32 PM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:21:01 PM</t>
+          <t>19 Sep 2026 02:58:09 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -15952,29 +16529,29 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>3h 22m</t>
+          <t>1h 51m</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TKT1338776</t>
+          <t>TKT1338726</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Maya shrestha</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -15994,22 +16571,22 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
+          <t>Case : YouTube not working   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:24:11 PM</t>
+          <t>19 Sep 2026 03:21:01 PM</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:29:31 PM</t>
+          <t>19 Sep 2026 11:58:53 AM</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:24:11 PM</t>
+          <t>19 Sep 2026 03:21:01 PM</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -16019,29 +16596,29 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>2h 54m</t>
+          <t>3h 22m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TKT1335765</t>
+          <t>TKT1338776</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>M.d  talibakhtar</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16061,22 +16638,22 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Slow internet    has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:29 PM</t>
+          <t>19 Sep 2026 03:24:11 PM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:31:48 PM</t>
+          <t>19 Sep 2026 12:29:31 PM</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:29 PM</t>
+          <t>19 Sep 2026 03:24:11 PM</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
@@ -16086,19 +16663,19 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>3d 1h 29m</t>
+          <t>2h 54m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>TKT1338801</t>
+          <t>TKT1335765</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Arpan Bahadur Singh</t>
+          <t>M.d  talibakhtar</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -16113,12 +16690,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -16128,32 +16705,32 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:53:26 PM</t>
+          <t>19 Sep 2026 04:01:29 PM</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:53:26 PM</t>
+          <t>16 Sep 2026 02:31:48 PM</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:01:06 PM</t>
+          <t>19 Sep 2026 04:01:29 PM</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>3h 7m</t>
+          <t>3d 1h 29m</t>
         </is>
       </c>
     </row>
@@ -16227,32 +16804,32 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>TKT1338779</t>
+          <t>TKT1338801</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Tenjin Tamang</t>
+          <t>Arpan Bahadur Singh</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 2.4Ghz</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -16262,99 +16839,300 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 router instal   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:33:53 PM</t>
+          <t>19 Sep 2026 12:53:26 PM</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:31:41 PM</t>
+          <t>19 Sep 2026 12:53:26 PM</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 04:33:53 PM</t>
+          <t>19 Sep 2026 04:01:06 PM</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 7m</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>4h 2m</t>
+          <t>3h 7m</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
+          <t>TKT1338779</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Tenjin Tamang</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 2.4Ghz</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : configure issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:31:41 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 04:33:53 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>TKT1337949</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Suresh Prasad Bhattarai</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 03:46:45 PM</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 03:46:45 PM</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 05:01:21 PM</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>1d 1h 14m</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M76" s="3" t="inlineStr">
         <is>
           <t>1d 1h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338977</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Nunulal Shah</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:02 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:38 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:02 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>1h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338823</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:29 PM</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:07:00 PM</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:10:29 PM</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>4h 3m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW70"/>
+  <dimension ref="A1:AW71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13043,10 +13043,8 @@
           <t>Nunulal Shah</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9851013999</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9851013999</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -13136,10 +13134,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
@@ -13150,7 +13146,7 @@
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
@@ -13246,10 +13242,8 @@
           <t>Sangita kunwar</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9843445345</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9843445345</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -13325,10 +13319,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH69" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH69" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
@@ -13351,10 +13343,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
@@ -13365,7 +13355,7 @@
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -13461,10 +13451,8 @@
           <t>Spandan Bhatta</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9823009955</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9823009955</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -13499,10 +13487,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y70" s="3" t="inlineStr">
-        <is>
-          <t>27.73269</t>
-        </is>
+      <c r="Y70" s="3" t="n">
+        <v>27.73269</v>
       </c>
       <c r="Z70" s="3" t="inlineStr">
         <is>
@@ -13558,48 +13544,251 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>85.29153</t>
-        </is>
+      <c r="AP70" s="3" t="n">
+        <v>85.29152999999999</v>
       </c>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>4h 3m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS70" s="3" t="inlineStr">
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:20 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338994</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Raju Shrestha</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Raju Shrestha</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9841446540</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:20:43 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9841446540</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:47:51 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:20:43 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.705933</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Mantar chowk bus stop, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr"/>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>01:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>L29-2</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.370967</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT70" s="3" t="inlineStr">
-        <is>
-          <t>4h 3m</t>
-        </is>
-      </c>
-      <c r="AU70" s="3" t="inlineStr">
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>1h 32m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV70" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW70" s="3" t="inlineStr">
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -13616,7 +13805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13653,7 +13842,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -13663,7 +13852,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -13674,7 +13863,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13875,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 41m</t>
+          <t>6h 32m</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13887,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 24m</t>
+          <t>1d 7h 42m</t>
         </is>
       </c>
     </row>
@@ -13739,14 +13928,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -13901,14 +14090,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17224,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -17102,14 +17291,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 05:10:29 PM</t>
@@ -17133,6 +17322,73 @@
       <c r="M78" s="3" t="inlineStr">
         <is>
           <t>4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338994</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Raju Shrestha</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:20:43 PM</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:47:51 PM</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:20:43 PM</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>1h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13654,10 +13654,8 @@
           <t>Raju Shrestha</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9841446540</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9841446540</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -13692,10 +13690,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.705933</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.705933</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -13747,25 +13743,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>L29-2</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.370967</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.37096699999999</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -13814,7 +13806,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17358,7 +17350,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW71"/>
+  <dimension ref="A1:AW73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13786,6 +13786,428 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:47 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338913</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Aarav  Bogati</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Aarav  Bogati</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9822772771</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:47:46 PM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9822772771</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:24:57 PM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:47:46 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>27.642374</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Radio Nepal Tower J8W4+RFH, karyabinayak 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>bogatiaarav@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>03:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>85.308388</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>3h 22m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 5:57 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338695</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Rana Magar</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Rana Magar</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9813211126</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:57:53 PM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9813211126</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:35:30 AM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:57:53 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr">
+        <is>
+          <t>27.7318</t>
+        </is>
+      </c>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>27.731802,85.359969,Kapan Faika, Budhanilkantha-, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>sunitarm40@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr">
+        <is>
+          <t>06:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>L49-6</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr">
+        <is>
+          <t>85.35997</t>
+        </is>
+      </c>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13797,7 +14219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13806,7 +14228,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13834,7 +14256,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -13844,7 +14266,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -13855,7 +14277,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
@@ -13867,7 +14289,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 32m</t>
+          <t>6h 15m</t>
         </is>
       </c>
     </row>
@@ -13879,7 +14301,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 42m</t>
+          <t>1d 6h 32m</t>
         </is>
       </c>
     </row>
@@ -13920,14 +14342,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -13938,14 +14360,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -14082,14 +14504,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -14151,10 +14573,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -17384,6 +17806,140 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338913</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Aarav  Bogati</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:47:46 PM</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:24:57 PM</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:47:46 PM</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>3h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338695</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Sunita Rana Magar</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:57:53 PM</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:35:30 AM</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:57:53 PM</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13853,10 +13853,8 @@
           <t>Aarav  Bogati</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9822772771</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9822772771</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -13891,10 +13889,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y72" s="3" t="inlineStr">
-        <is>
-          <t>27.642374</t>
-        </is>
+      <c r="Y72" s="3" t="n">
+        <v>27.642374</v>
       </c>
       <c r="Z72" s="3" t="inlineStr">
         <is>
@@ -13950,25 +13946,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>85.308388</t>
-        </is>
+      <c r="AP72" s="3" t="n">
+        <v>85.30838799999999</v>
       </c>
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
@@ -14064,10 +14056,8 @@
           <t>Sunita Rana Magar</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9813211126</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9813211126</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -14102,10 +14092,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y73" s="3" t="inlineStr">
-        <is>
-          <t>27.7318</t>
-        </is>
+      <c r="Y73" s="3" t="n">
+        <v>27.7318</v>
       </c>
       <c r="Z73" s="3" t="inlineStr">
         <is>
@@ -14161,25 +14149,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
           <t>L49-6</t>
         </is>
       </c>
-      <c r="AP73" s="3" t="inlineStr">
-        <is>
-          <t>85.35997</t>
-        </is>
+      <c r="AP73" s="3" t="n">
+        <v>85.35997</v>
       </c>
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
@@ -14228,7 +14212,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17839,7 +17823,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -17906,7 +17890,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
